--- a/event_registration_forms/028_temporary_public_art_structure_application_form--event_registration_forms.xlsx
+++ b/event_registration_forms/028_temporary_public_art_structure_application_form--event_registration_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>organization_name</t>
+          <t>organization_name_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Organization Name</t>
+          <t>Organization Name 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>artist_statement</t>
+          <t>artist_statement_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Artist Statement</t>
+          <t>Artist Statement 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>artist_name</t>
+          <t>artist_name_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Artist Name</t>
+          <t>Artist Name 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>artist_name</t>
+          <t>artist_name_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Artist Name</t>
+          <t>Artist Name 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>artist_statement</t>
+          <t>artist_statement_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Artist Statement</t>
+          <t>Artist Statement 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
